--- a/The_Alternative_F1.xlsx
+++ b/The_Alternative_F1.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2398" uniqueCount="436">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2462" uniqueCount="435">
   <si>
     <t>Positions</t>
   </si>
@@ -1225,9 +1225,6 @@
   </si>
   <si>
     <t>TBD2</t>
-  </si>
-  <si>
-    <t>Jario</t>
   </si>
   <si>
     <t>Randy</t>
@@ -2887,15 +2884,27 @@
         <f>IFERROR((VLOOKUP(K2,Scoring!$A:$B,2,0))+IF(M2="y",1,0)+IF(N2="y",1,0)+IF(O2="y",1,0)+IF(P2="y",1,0),0)</f>
         <v>22</v>
       </c>
-      <c r="R2" s="16"/>
-      <c r="S2" s="17"/>
-      <c r="T2" s="18"/>
-      <c r="U2" s="19"/>
-      <c r="V2" s="20"/>
-      <c r="W2" s="21"/>
+      <c r="R2" s="16">
+        <v>16.0</v>
+      </c>
+      <c r="S2" s="17">
+        <v>16.0</v>
+      </c>
+      <c r="T2" s="18" t="s">
+        <v>129</v>
+      </c>
+      <c r="U2" s="19" t="s">
+        <v>129</v>
+      </c>
+      <c r="V2" s="20" t="s">
+        <v>129</v>
+      </c>
+      <c r="W2" s="21" t="s">
+        <v>129</v>
+      </c>
       <c r="X2" s="71">
         <f>IFERROR((VLOOKUP(R2,Scoring!$A:$B,2,0))+IF(T2="y",1,0)+IF(U2="y",1,0)+IF(V2="y",1,0)+IF(W2="y",1,0),0)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Y2" s="16"/>
       <c r="Z2" s="17"/>
@@ -3065,15 +3074,27 @@
         <f>IFERROR((VLOOKUP(K3,Scoring!$A:$B,2,0))+IF(M3="y",1,0)+IF(N3="y",1,0)+IF(O3="y",1,0)+IF(P3="y",1,0),0)</f>
         <v>12</v>
       </c>
-      <c r="R3" s="24"/>
-      <c r="S3" s="25"/>
-      <c r="T3" s="26"/>
-      <c r="U3" s="27"/>
-      <c r="V3" s="28"/>
-      <c r="W3" s="29"/>
+      <c r="R3" s="24">
+        <v>14.0</v>
+      </c>
+      <c r="S3" s="25">
+        <v>14.0</v>
+      </c>
+      <c r="T3" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="U3" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="V3" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="W3" s="29" t="s">
+        <v>128</v>
+      </c>
       <c r="X3" s="72">
         <f>IFERROR((VLOOKUP(R3,Scoring!$A:$B,2,0))+IF(T3="y",1,0)+IF(U3="y",1,0)+IF(V3="y",1,0)+IF(W3="y",1,0),0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y3" s="24"/>
       <c r="Z3" s="25"/>
@@ -3243,15 +3264,27 @@
         <f>IFERROR((VLOOKUP(K4,Scoring!$A:$B,2,0))+IF(M4="y",1,0)+IF(N4="y",1,0)+IF(O4="y",1,0)+IF(P4="y",1,0),0)</f>
         <v>8</v>
       </c>
-      <c r="R4" s="36"/>
-      <c r="S4" s="37"/>
-      <c r="T4" s="38"/>
-      <c r="U4" s="39"/>
-      <c r="V4" s="40"/>
-      <c r="W4" s="41"/>
+      <c r="R4" s="36">
+        <v>12.0</v>
+      </c>
+      <c r="S4" s="37">
+        <v>12.0</v>
+      </c>
+      <c r="T4" s="38" t="s">
+        <v>128</v>
+      </c>
+      <c r="U4" s="39" t="s">
+        <v>128</v>
+      </c>
+      <c r="V4" s="40" t="s">
+        <v>128</v>
+      </c>
+      <c r="W4" s="41" t="s">
+        <v>128</v>
+      </c>
       <c r="X4" s="71">
         <f>IFERROR((VLOOKUP(R4,Scoring!$A:$B,2,0))+IF(T4="y",1,0)+IF(U4="y",1,0)+IF(V4="y",1,0)+IF(W4="y",1,0),0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y4" s="36"/>
       <c r="Z4" s="37"/>
@@ -3421,15 +3454,27 @@
         <f>IFERROR((VLOOKUP(K5,Scoring!$A:$B,2,0))+IF(M5="y",1,0)+IF(N5="y",1,0)+IF(O5="y",1,0)+IF(P5="y",1,0),0)</f>
         <v>4</v>
       </c>
-      <c r="R5" s="48"/>
-      <c r="S5" s="49"/>
-      <c r="T5" s="50"/>
-      <c r="U5" s="51"/>
-      <c r="V5" s="52"/>
-      <c r="W5" s="53"/>
+      <c r="R5" s="48">
+        <v>10.0</v>
+      </c>
+      <c r="S5" s="49">
+        <v>10.0</v>
+      </c>
+      <c r="T5" s="50" t="s">
+        <v>128</v>
+      </c>
+      <c r="U5" s="51" t="s">
+        <v>128</v>
+      </c>
+      <c r="V5" s="52" t="s">
+        <v>128</v>
+      </c>
+      <c r="W5" s="53" t="s">
+        <v>128</v>
+      </c>
       <c r="X5" s="72">
         <f>IFERROR((VLOOKUP(R5,Scoring!$A:$B,2,0))+IF(T5="y",1,0)+IF(U5="y",1,0)+IF(V5="y",1,0)+IF(W5="y",1,0),0)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y5" s="48"/>
       <c r="Z5" s="49"/>
@@ -3599,15 +3644,27 @@
         <f>IFERROR((VLOOKUP(K6,Scoring!$A:$B,2,0))+IF(M6="y",1,0)+IF(N6="y",1,0)+IF(O6="y",1,0)+IF(P6="y",1,0),0)</f>
         <v>2</v>
       </c>
-      <c r="R6" s="24"/>
-      <c r="S6" s="25"/>
-      <c r="T6" s="26"/>
-      <c r="U6" s="27"/>
-      <c r="V6" s="28"/>
-      <c r="W6" s="29"/>
+      <c r="R6" s="24">
+        <v>8.0</v>
+      </c>
+      <c r="S6" s="25">
+        <v>8.0</v>
+      </c>
+      <c r="T6" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="U6" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="V6" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="W6" s="29" t="s">
+        <v>128</v>
+      </c>
       <c r="X6" s="71">
         <f>IFERROR((VLOOKUP(R6,Scoring!$A:$B,2,0))+IF(T6="y",1,0)+IF(U6="y",1,0)+IF(V6="y",1,0)+IF(W6="y",1,0),0)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y6" s="24"/>
       <c r="Z6" s="25"/>
@@ -3777,15 +3834,27 @@
         <f>IFERROR((VLOOKUP(K7,Scoring!$A:$B,2,0))+IF(M7="y",1,0)+IF(N7="y",1,0)+IF(O7="y",1,0)+IF(P7="y",1,0),0)</f>
         <v>1</v>
       </c>
-      <c r="R7" s="24"/>
-      <c r="S7" s="25"/>
-      <c r="T7" s="26"/>
-      <c r="U7" s="27"/>
-      <c r="V7" s="28"/>
-      <c r="W7" s="29"/>
+      <c r="R7" s="24">
+        <v>6.0</v>
+      </c>
+      <c r="S7" s="25">
+        <v>6.0</v>
+      </c>
+      <c r="T7" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="U7" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="V7" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="W7" s="29" t="s">
+        <v>128</v>
+      </c>
       <c r="X7" s="72">
         <f>IFERROR((VLOOKUP(R7,Scoring!$A:$B,2,0))+IF(T7="y",1,0)+IF(U7="y",1,0)+IF(V7="y",1,0)+IF(W7="y",1,0),0)</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Y7" s="24"/>
       <c r="Z7" s="25"/>
@@ -3955,15 +4024,27 @@
         <f>IFERROR((VLOOKUP(K8,Scoring!$A:$B,2,0))+IF(M8="y",1,0)+IF(N8="y",1,0)+IF(O8="y",1,0)+IF(P8="y",1,0),0)</f>
         <v>1</v>
       </c>
-      <c r="R8" s="36"/>
-      <c r="S8" s="37"/>
-      <c r="T8" s="38"/>
-      <c r="U8" s="39"/>
-      <c r="V8" s="40"/>
-      <c r="W8" s="41"/>
+      <c r="R8" s="36">
+        <v>4.0</v>
+      </c>
+      <c r="S8" s="37">
+        <v>4.0</v>
+      </c>
+      <c r="T8" s="38" t="s">
+        <v>128</v>
+      </c>
+      <c r="U8" s="39" t="s">
+        <v>128</v>
+      </c>
+      <c r="V8" s="40" t="s">
+        <v>128</v>
+      </c>
+      <c r="W8" s="41" t="s">
+        <v>128</v>
+      </c>
       <c r="X8" s="71">
         <f>IFERROR((VLOOKUP(R8,Scoring!$A:$B,2,0))+IF(T8="y",1,0)+IF(U8="y",1,0)+IF(V8="y",1,0)+IF(W8="y",1,0),0)</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Y8" s="36"/>
       <c r="Z8" s="37"/>
@@ -4133,15 +4214,27 @@
         <f>IFERROR((VLOOKUP(K9,Scoring!$A:$B,2,0))+IF(M9="y",1,0)+IF(N9="y",1,0)+IF(O9="y",1,0)+IF(P9="y",1,0),0)</f>
         <v>1</v>
       </c>
-      <c r="R9" s="48"/>
-      <c r="S9" s="49"/>
-      <c r="T9" s="50"/>
-      <c r="U9" s="51"/>
-      <c r="V9" s="52"/>
-      <c r="W9" s="53"/>
+      <c r="R9" s="48">
+        <v>2.0</v>
+      </c>
+      <c r="S9" s="49">
+        <v>2.0</v>
+      </c>
+      <c r="T9" s="50" t="s">
+        <v>128</v>
+      </c>
+      <c r="U9" s="51" t="s">
+        <v>128</v>
+      </c>
+      <c r="V9" s="52" t="s">
+        <v>128</v>
+      </c>
+      <c r="W9" s="53" t="s">
+        <v>128</v>
+      </c>
       <c r="X9" s="72">
         <f>IFERROR((VLOOKUP(R9,Scoring!$A:$B,2,0))+IF(T9="y",1,0)+IF(U9="y",1,0)+IF(V9="y",1,0)+IF(W9="y",1,0),0)</f>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="Y9" s="48"/>
       <c r="Z9" s="49"/>
@@ -4311,15 +4404,27 @@
         <f>IFERROR((VLOOKUP(K10,Scoring!$A:$B,2,0))+IF(M10="y",1,0)+IF(N10="y",1,0)+IF(O10="y",1,0)+IF(P10="y",1,0),0)</f>
         <v>25</v>
       </c>
-      <c r="R10" s="24"/>
-      <c r="S10" s="25"/>
-      <c r="T10" s="26"/>
-      <c r="U10" s="27"/>
-      <c r="V10" s="28"/>
-      <c r="W10" s="29"/>
+      <c r="R10" s="24">
+        <v>15.0</v>
+      </c>
+      <c r="S10" s="25">
+        <v>1.0</v>
+      </c>
+      <c r="T10" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="U10" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="V10" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="W10" s="29" t="s">
+        <v>128</v>
+      </c>
       <c r="X10" s="71">
         <f>IFERROR((VLOOKUP(R10,Scoring!$A:$B,2,0))+IF(T10="y",1,0)+IF(U10="y",1,0)+IF(V10="y",1,0)+IF(W10="y",1,0),0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y10" s="24"/>
       <c r="Z10" s="25"/>
@@ -4489,15 +4594,27 @@
         <f>IFERROR((VLOOKUP(K11,Scoring!$A:$B,2,0))+IF(M11="y",1,0)+IF(N11="y",1,0)+IF(O11="y",1,0)+IF(P11="y",1,0),0)</f>
         <v>15</v>
       </c>
-      <c r="R11" s="24"/>
-      <c r="S11" s="25"/>
-      <c r="T11" s="26"/>
-      <c r="U11" s="27"/>
-      <c r="V11" s="28"/>
-      <c r="W11" s="29"/>
+      <c r="R11" s="24">
+        <v>13.0</v>
+      </c>
+      <c r="S11" s="25">
+        <v>3.0</v>
+      </c>
+      <c r="T11" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="U11" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="V11" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="W11" s="29" t="s">
+        <v>128</v>
+      </c>
       <c r="X11" s="72">
         <f>IFERROR((VLOOKUP(R11,Scoring!$A:$B,2,0))+IF(T11="y",1,0)+IF(U11="y",1,0)+IF(V11="y",1,0)+IF(W11="y",1,0),0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y11" s="24"/>
       <c r="Z11" s="25"/>
@@ -4667,15 +4784,27 @@
         <f>IFERROR((VLOOKUP(K12,Scoring!$A:$B,2,0))+IF(M12="y",1,0)+IF(N12="y",1,0)+IF(O12="y",1,0)+IF(P12="y",1,0),0)</f>
         <v>10</v>
       </c>
-      <c r="R12" s="36"/>
-      <c r="S12" s="37"/>
-      <c r="T12" s="38"/>
-      <c r="U12" s="39"/>
-      <c r="V12" s="40"/>
-      <c r="W12" s="41"/>
+      <c r="R12" s="36">
+        <v>11.0</v>
+      </c>
+      <c r="S12" s="37">
+        <v>5.0</v>
+      </c>
+      <c r="T12" s="38" t="s">
+        <v>128</v>
+      </c>
+      <c r="U12" s="39" t="s">
+        <v>128</v>
+      </c>
+      <c r="V12" s="40" t="s">
+        <v>128</v>
+      </c>
+      <c r="W12" s="41" t="s">
+        <v>128</v>
+      </c>
       <c r="X12" s="71">
         <f>IFERROR((VLOOKUP(R12,Scoring!$A:$B,2,0))+IF(T12="y",1,0)+IF(U12="y",1,0)+IF(V12="y",1,0)+IF(W12="y",1,0),0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y12" s="36"/>
       <c r="Z12" s="37"/>
@@ -4845,15 +4974,27 @@
         <f>IFERROR((VLOOKUP(K13,Scoring!$A:$B,2,0))+IF(M13="y",1,0)+IF(N13="y",1,0)+IF(O13="y",1,0)+IF(P13="y",1,0),0)</f>
         <v>6</v>
       </c>
-      <c r="R13" s="24"/>
-      <c r="S13" s="25"/>
-      <c r="T13" s="26"/>
-      <c r="U13" s="27"/>
-      <c r="V13" s="28"/>
-      <c r="W13" s="29"/>
+      <c r="R13" s="24">
+        <v>9.0</v>
+      </c>
+      <c r="S13" s="25">
+        <v>7.0</v>
+      </c>
+      <c r="T13" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="U13" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="V13" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="W13" s="29" t="s">
+        <v>128</v>
+      </c>
       <c r="X13" s="72">
         <f>IFERROR((VLOOKUP(R13,Scoring!$A:$B,2,0))+IF(T13="y",1,0)+IF(U13="y",1,0)+IF(V13="y",1,0)+IF(W13="y",1,0),0)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y13" s="24"/>
       <c r="Z13" s="25"/>
@@ -5023,15 +5164,27 @@
         <f>IFERROR((VLOOKUP(K14,Scoring!$A:$B,2,0))+IF(M14="y",1,0)+IF(N14="y",1,0)+IF(O14="y",1,0)+IF(P14="y",1,0),0)</f>
         <v>3</v>
       </c>
-      <c r="R14" s="36"/>
-      <c r="S14" s="37"/>
-      <c r="T14" s="38"/>
-      <c r="U14" s="39"/>
-      <c r="V14" s="40"/>
-      <c r="W14" s="41"/>
+      <c r="R14" s="36">
+        <v>7.0</v>
+      </c>
+      <c r="S14" s="37">
+        <v>9.0</v>
+      </c>
+      <c r="T14" s="38" t="s">
+        <v>128</v>
+      </c>
+      <c r="U14" s="39" t="s">
+        <v>128</v>
+      </c>
+      <c r="V14" s="40" t="s">
+        <v>128</v>
+      </c>
+      <c r="W14" s="41" t="s">
+        <v>128</v>
+      </c>
       <c r="X14" s="71">
         <f>IFERROR((VLOOKUP(R14,Scoring!$A:$B,2,0))+IF(T14="y",1,0)+IF(U14="y",1,0)+IF(V14="y",1,0)+IF(W14="y",1,0),0)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Y14" s="36"/>
       <c r="Z14" s="37"/>
@@ -5201,15 +5354,27 @@
         <f>IFERROR((VLOOKUP(K15,Scoring!$A:$B,2,0))+IF(M15="y",1,0)+IF(N15="y",1,0)+IF(O15="y",1,0)+IF(P15="y",1,0),0)</f>
         <v>1</v>
       </c>
-      <c r="R15" s="48"/>
-      <c r="S15" s="49"/>
-      <c r="T15" s="50"/>
-      <c r="U15" s="51"/>
-      <c r="V15" s="52"/>
-      <c r="W15" s="53"/>
+      <c r="R15" s="48">
+        <v>5.0</v>
+      </c>
+      <c r="S15" s="49">
+        <v>11.0</v>
+      </c>
+      <c r="T15" s="50" t="s">
+        <v>128</v>
+      </c>
+      <c r="U15" s="51" t="s">
+        <v>128</v>
+      </c>
+      <c r="V15" s="52" t="s">
+        <v>128</v>
+      </c>
+      <c r="W15" s="53" t="s">
+        <v>128</v>
+      </c>
       <c r="X15" s="72">
         <f>IFERROR((VLOOKUP(R15,Scoring!$A:$B,2,0))+IF(T15="y",1,0)+IF(U15="y",1,0)+IF(V15="y",1,0)+IF(W15="y",1,0),0)</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Y15" s="48"/>
       <c r="Z15" s="49"/>
@@ -5330,7 +5495,7 @@
         <v>41</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>401</v>
+        <v>44</v>
       </c>
       <c r="C16" s="15" t="s">
         <v>45</v>
@@ -5379,15 +5544,27 @@
         <f>IFERROR((VLOOKUP(K16,Scoring!$A:$B,2,0))+IF(M16="y",1,0)+IF(N16="y",1,0)+IF(O16="y",1,0)+IF(P16="y",1,0),0)</f>
         <v>1</v>
       </c>
-      <c r="R16" s="24"/>
-      <c r="S16" s="25"/>
-      <c r="T16" s="26"/>
-      <c r="U16" s="27"/>
-      <c r="V16" s="28"/>
-      <c r="W16" s="29"/>
+      <c r="R16" s="24">
+        <v>3.0</v>
+      </c>
+      <c r="S16" s="25">
+        <v>13.0</v>
+      </c>
+      <c r="T16" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="U16" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="V16" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="W16" s="29" t="s">
+        <v>128</v>
+      </c>
       <c r="X16" s="71">
         <f>IFERROR((VLOOKUP(R16,Scoring!$A:$B,2,0))+IF(T16="y",1,0)+IF(U16="y",1,0)+IF(V16="y",1,0)+IF(W16="y",1,0),0)</f>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Y16" s="24"/>
       <c r="Z16" s="25"/>
@@ -5508,7 +5685,7 @@
         <v>41</v>
       </c>
       <c r="B17" s="58" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C17" s="59" t="s">
         <v>395</v>
@@ -5557,15 +5734,27 @@
         <f>IFERROR((VLOOKUP(K17,Scoring!$A:$B,2,0))+IF(M17="y",1,0)+IF(N17="y",1,0)+IF(O17="y",1,0)+IF(P17="y",1,0),0)</f>
         <v>1</v>
       </c>
-      <c r="R17" s="60"/>
-      <c r="S17" s="61"/>
-      <c r="T17" s="62"/>
-      <c r="U17" s="63"/>
-      <c r="V17" s="64"/>
-      <c r="W17" s="65"/>
+      <c r="R17" s="60">
+        <v>1.0</v>
+      </c>
+      <c r="S17" s="61">
+        <v>15.0</v>
+      </c>
+      <c r="T17" s="62" t="s">
+        <v>128</v>
+      </c>
+      <c r="U17" s="63" t="s">
+        <v>128</v>
+      </c>
+      <c r="V17" s="64" t="s">
+        <v>128</v>
+      </c>
+      <c r="W17" s="65" t="s">
+        <v>128</v>
+      </c>
       <c r="X17" s="73">
         <f>IFERROR((VLOOKUP(R17,Scoring!$A:$B,2,0))+IF(T17="y",1,0)+IF(U17="y",1,0)+IF(V17="y",1,0)+IF(W17="y",1,0),0)</f>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="Y17" s="60"/>
       <c r="Z17" s="61"/>
@@ -5709,10 +5898,10 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="B2" s="69" t="s">
         <v>403</v>
-      </c>
-      <c r="B2" s="69" t="s">
-        <v>404</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>292</v>
@@ -5720,10 +5909,10 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B3" s="69" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>292</v>
@@ -5731,10 +5920,10 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B4" s="69" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>292</v>
@@ -5742,10 +5931,10 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="B5" s="69" t="s">
         <v>407</v>
-      </c>
-      <c r="B5" s="69" t="s">
-        <v>408</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>292</v>
@@ -5753,10 +5942,10 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="B6" s="69" t="s">
         <v>409</v>
-      </c>
-      <c r="B6" s="69" t="s">
-        <v>410</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>292</v>
@@ -5764,10 +5953,10 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="B7" s="69" t="s">
         <v>411</v>
-      </c>
-      <c r="B7" s="69" t="s">
-        <v>412</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>292</v>
@@ -5775,10 +5964,10 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="B8" s="69" t="s">
         <v>413</v>
-      </c>
-      <c r="B8" s="69" t="s">
-        <v>414</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>292</v>
@@ -5786,10 +5975,10 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="B9" s="69" t="s">
         <v>415</v>
-      </c>
-      <c r="B9" s="69" t="s">
-        <v>416</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>292</v>
@@ -5797,10 +5986,10 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="B10" s="69" t="s">
         <v>417</v>
-      </c>
-      <c r="B10" s="69" t="s">
-        <v>418</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>292</v>
@@ -5808,10 +5997,10 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="B11" s="69" t="s">
         <v>419</v>
-      </c>
-      <c r="B11" s="69" t="s">
-        <v>420</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>292</v>
@@ -5819,10 +6008,10 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="B12" s="69" t="s">
         <v>421</v>
-      </c>
-      <c r="B12" s="69" t="s">
-        <v>422</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>292</v>
@@ -5830,10 +6019,10 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="B13" s="69" t="s">
         <v>423</v>
-      </c>
-      <c r="B13" s="69" t="s">
-        <v>424</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>292</v>
@@ -5841,10 +6030,10 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="B14" s="69" t="s">
         <v>425</v>
-      </c>
-      <c r="B14" s="69" t="s">
-        <v>426</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>292</v>
@@ -5852,10 +6041,10 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="B15" s="69" t="s">
         <v>427</v>
-      </c>
-      <c r="B15" s="69" t="s">
-        <v>428</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>292</v>
@@ -5863,10 +6052,10 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="B16" s="69" t="s">
         <v>429</v>
-      </c>
-      <c r="B16" s="69" t="s">
-        <v>430</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>292</v>
@@ -5874,10 +6063,10 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="B17" s="69" t="s">
         <v>431</v>
-      </c>
-      <c r="B17" s="69" t="s">
-        <v>432</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>292</v>
@@ -5885,10 +6074,10 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="B18" s="69" t="s">
         <v>433</v>
-      </c>
-      <c r="B18" s="69" t="s">
-        <v>434</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>292</v>
@@ -5899,7 +6088,7 @@
         <v>294</v>
       </c>
       <c r="B19" s="69" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>292</v>
